--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1020,6 +1020,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1029,7 +1032,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1359,6 +1362,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>220000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>222000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1401,7 +1407,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1731,6 +1737,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1740,7 +1749,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2070,6 +2079,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>542783.95352470258</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>613430.1755816536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2112,7 +2124,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2442,6 +2454,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2451,7 +2466,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2781,6 +2796,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>322783.95352470258</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>391430.1755816536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2802,11 +2820,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399528320"/>
-        <c:axId val="399839232"/>
+        <c:axId val="466793216"/>
+        <c:axId val="466973056"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399528320"/>
+        <c:axId val="466793216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2846,14 +2864,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399839232"/>
+        <c:crossAx val="466973056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399839232"/>
+        <c:axId val="466973056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2902,7 +2920,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399528320"/>
+        <c:crossAx val="466793216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3032,7 +3050,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3362,6 +3380,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3371,7 +3392,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3701,6 +3722,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>220000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>222000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3734,7 +3758,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4064,6 +4088,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4073,7 +4100,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4403,6 +4430,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>542783.95352470258</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>613430.1755816536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4436,7 +4466,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4766,6 +4796,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4775,7 +4808,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5105,6 +5138,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>322783.95352470258</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>391430.1755816536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5126,11 +5162,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426837504"/>
-        <c:axId val="426839424"/>
+        <c:axId val="470371328"/>
+        <c:axId val="470383232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426837504"/>
+        <c:axId val="470371328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5140,14 +5176,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426839424"/>
+        <c:crossAx val="470383232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426839424"/>
+        <c:axId val="470383232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5158,7 +5194,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426837504"/>
+        <c:crossAx val="470371328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5276,7 +5312,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5606,6 +5642,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5615,7 +5654,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5945,6 +5984,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>229000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5987,7 +6029,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6317,6 +6359,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6326,7 +6371,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6656,6 +6701,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>567445.53608854045</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>641210.7237338433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6698,7 +6746,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7028,6 +7076,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7037,7 +7088,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7367,6 +7418,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>340445.53608854045</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>412210.7237338433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7388,11 +7442,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="456520448"/>
-        <c:axId val="456522752"/>
+        <c:axId val="510644992"/>
+        <c:axId val="510646528"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="456520448"/>
+        <c:axId val="510644992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7432,14 +7486,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="456522752"/>
+        <c:crossAx val="510646528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="456522752"/>
+        <c:axId val="510646528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7488,7 +7542,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="456520448"/>
+        <c:crossAx val="510644992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7618,7 +7672,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7948,6 +8002,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7957,7 +8014,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8287,6 +8344,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>229000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8320,7 +8380,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8650,6 +8710,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8659,7 +8722,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8989,6 +9052,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>567445.53608854045</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>641210.7237338433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9022,7 +9088,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9352,6 +9418,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9361,7 +9430,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9691,6 +9760,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>340445.53608854045</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>412210.7237338433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9712,11 +9784,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479673344"/>
-        <c:axId val="497464064"/>
+        <c:axId val="510805120"/>
+        <c:axId val="510806656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479673344"/>
+        <c:axId val="510805120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9726,14 +9798,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="497464064"/>
+        <c:crossAx val="510806656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="497464064"/>
+        <c:axId val="510806656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9744,7 +9816,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="479673344"/>
+        <c:crossAx val="510805120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9862,7 +9934,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10192,6 +10264,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10201,7 +10276,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10531,6 +10606,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>229000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10573,7 +10651,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10903,6 +10981,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10912,7 +10993,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11242,6 +11323,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>565611.67845160083</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>639144.93698818795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11284,7 +11368,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11614,6 +11698,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11623,7 +11710,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11953,6 +12040,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>338611.67845160083</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>410144.93698818795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11974,11 +12064,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="610502144"/>
-        <c:axId val="610503680"/>
+        <c:axId val="511477632"/>
+        <c:axId val="511479168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="610502144"/>
+        <c:axId val="511477632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12018,14 +12108,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="610503680"/>
+        <c:crossAx val="511479168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="610503680"/>
+        <c:axId val="511479168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12074,7 +12164,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="610502144"/>
+        <c:crossAx val="511477632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12204,7 +12294,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12534,6 +12624,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12543,7 +12636,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12873,6 +12966,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>227000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>229000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12906,7 +13002,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13236,6 +13332,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13245,7 +13344,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13575,6 +13674,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>565611.67845160083</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>639144.93698818795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13608,7 +13710,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13938,6 +14040,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13947,7 +14052,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14277,6 +14382,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>338611.67845160083</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>410144.93698818795</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14298,11 +14406,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="497432448"/>
-        <c:axId val="497433984"/>
+        <c:axId val="511650048"/>
+        <c:axId val="511655936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="497432448"/>
+        <c:axId val="511650048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14312,14 +14420,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="497433984"/>
+        <c:crossAx val="511655936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="497433984"/>
+        <c:axId val="511655936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14330,7 +14438,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="497432448"/>
+        <c:crossAx val="511650048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14372,7 +14480,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14410,7 +14518,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14451,7 +14559,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14489,7 +14597,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14532,7 +14640,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14570,7 +14678,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14848,7 +14956,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14857,7 +14965,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB112"/>
+  <dimension ref="A1:AB113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18811,6 +18919,35 @@
         <v>322783.95352470258</v>
       </c>
     </row>
+    <row r="113" spans="1:9" ht="12.75">
+      <c r="A113" s="13">
+        <v>46203</v>
+      </c>
+      <c r="B113" s="18">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C113" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D113" s="15">
+        <v>580.21467493663954</v>
+      </c>
+      <c r="E113" s="15">
+        <v>177960.59496071746</v>
+      </c>
+      <c r="F113" s="15">
+        <v>613430.1755816536</v>
+      </c>
+      <c r="G113" s="15">
+        <v>222000</v>
+      </c>
+      <c r="H113" s="15">
+        <v>613430.1755816536</v>
+      </c>
+      <c r="I113" s="15">
+        <v>391430.1755816536</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18822,7 +18959,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24493,6 +24630,50 @@
         <v>74.805935689687729</v>
       </c>
     </row>
+    <row r="113" spans="1:14" ht="12.75">
+      <c r="A113" s="13">
+        <v>46203</v>
+      </c>
+      <c r="B113" s="18">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C113" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D113" s="15">
+        <v>580.21467493663954</v>
+      </c>
+      <c r="E113" s="15">
+        <v>186019.93581855964</v>
+      </c>
+      <c r="F113" s="15">
+        <v>641210.7237338433</v>
+      </c>
+      <c r="G113" s="15">
+        <v>229000</v>
+      </c>
+      <c r="H113" s="15">
+        <v>641210.7237338433</v>
+      </c>
+      <c r="I113" s="15">
+        <v>412210.7237338433</v>
+      </c>
+      <c r="J113" s="21">
+        <v>0.38700008392333984</v>
+      </c>
+      <c r="K113" s="21">
+        <v>0.22298399794060811</v>
+      </c>
+      <c r="L113" s="21">
+        <v>0.38700008392333984</v>
+      </c>
+      <c r="M113" s="23">
+        <v>0.27636018590033579</v>
+      </c>
+      <c r="N113" s="21">
+        <v>80.686006638099158</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24504,7 +24685,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -31052,6 +31233,59 @@
         <v>90.125507288989468</v>
       </c>
     </row>
+    <row r="113" spans="1:17" ht="12.75">
+      <c r="A113" s="13">
+        <v>46203</v>
+      </c>
+      <c r="B113" s="18">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C113" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D113" s="15">
+        <v>580.21467493663954</v>
+      </c>
+      <c r="E113" s="15">
+        <v>185420.63592600022</v>
+      </c>
+      <c r="F113" s="15">
+        <v>639144.93698818795</v>
+      </c>
+      <c r="G113" s="15">
+        <v>229000</v>
+      </c>
+      <c r="H113" s="15">
+        <v>639144.93698818795</v>
+      </c>
+      <c r="I113" s="15">
+        <v>410144.93698818795</v>
+      </c>
+      <c r="J113" s="15">
+        <v>3.4479999542236328</v>
+      </c>
+      <c r="K113" s="15">
+        <v>2.8849999904632568</v>
+      </c>
+      <c r="L113" s="19">
+        <v>3.4479999542236328</v>
+      </c>
+      <c r="M113" s="19">
+        <v>2.1180000305175781</v>
+      </c>
+      <c r="N113" s="21">
+        <v>99.924817475329945</v>
+      </c>
+      <c r="O113" s="21">
+        <v>87.572495182046978</v>
+      </c>
+      <c r="P113" s="21">
+        <v>80.545329999757996</v>
+      </c>
+      <c r="Q113" s="21">
+        <v>101.62682554662496</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1023,6 +1023,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1032,7 +1035,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1365,6 +1368,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>222000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>224000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1407,7 +1413,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1740,6 +1746,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1749,7 +1758,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2082,6 +2091,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>613430.1755816536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>500823.54292283044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2124,7 +2136,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2457,6 +2469,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2466,7 +2481,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2799,6 +2814,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>391430.1755816536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>276823.54292283044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2820,11 +2838,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="466793216"/>
-        <c:axId val="466973056"/>
+        <c:axId val="582754688"/>
+        <c:axId val="582756224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="466793216"/>
+        <c:axId val="582754688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2864,14 +2882,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466973056"/>
+        <c:crossAx val="582756224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466973056"/>
+        <c:axId val="582756224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2920,7 +2938,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466793216"/>
+        <c:crossAx val="582754688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3050,7 +3068,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3383,6 +3401,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3392,7 +3413,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3725,6 +3746,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>222000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>224000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3758,7 +3782,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4091,6 +4115,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4100,7 +4127,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4433,6 +4460,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>613430.1755816536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>500823.54292283044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4466,7 +4496,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4799,6 +4829,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4808,7 +4841,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5141,6 +5174,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>391430.1755816536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>276823.54292283044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5162,11 +5198,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="470371328"/>
-        <c:axId val="470383232"/>
+        <c:axId val="678418688"/>
+        <c:axId val="548163584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="470371328"/>
+        <c:axId val="678418688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5176,14 +5212,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="470383232"/>
+        <c:crossAx val="548163584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="470383232"/>
+        <c:axId val="548163584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5194,7 +5230,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="470371328"/>
+        <c:crossAx val="678418688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5312,7 +5348,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5645,6 +5681,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5654,7 +5693,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5987,6 +6026,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>231000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6029,7 +6071,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6362,6 +6404,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6371,7 +6416,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6704,6 +6749,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>641210.7237338433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>523413.87513215444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6746,7 +6794,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7079,6 +7127,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7088,7 +7139,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7421,6 +7472,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>412210.7237338433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>292413.87513215444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7442,11 +7496,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="510644992"/>
-        <c:axId val="510646528"/>
+        <c:axId val="548191232"/>
+        <c:axId val="548193024"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="510644992"/>
+        <c:axId val="548191232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7486,14 +7540,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510646528"/>
+        <c:crossAx val="548193024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="510646528"/>
+        <c:axId val="548193024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7542,7 +7596,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510644992"/>
+        <c:crossAx val="548191232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7672,7 +7726,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8005,6 +8059,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8014,7 +8071,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8347,6 +8404,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>231000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8380,7 +8440,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8713,6 +8773,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8722,7 +8785,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9055,6 +9118,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>641210.7237338433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>523413.87513215444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9088,7 +9154,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9421,6 +9487,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9430,7 +9499,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9763,6 +9832,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>412210.7237338433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>292413.87513215444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9784,11 +9856,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="510805120"/>
-        <c:axId val="510806656"/>
+        <c:axId val="547692544"/>
+        <c:axId val="547694080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="510805120"/>
+        <c:axId val="547692544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9798,14 +9870,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="510806656"/>
+        <c:crossAx val="547694080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="510806656"/>
+        <c:axId val="547694080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9816,7 +9888,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="510805120"/>
+        <c:crossAx val="547692544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9934,7 +10006,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10267,6 +10339,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10276,7 +10351,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10609,6 +10684,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>231000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10651,7 +10729,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10984,6 +11062,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10993,7 +11074,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11326,6 +11407,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>639144.93698818795</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>521734.03754931345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11368,7 +11452,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11701,6 +11785,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11710,7 +11797,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12043,6 +12130,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>410144.93698818795</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>290734.03754931345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12064,11 +12154,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="511477632"/>
-        <c:axId val="511479168"/>
+        <c:axId val="547963648"/>
+        <c:axId val="547965184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="511477632"/>
+        <c:axId val="547963648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12108,14 +12198,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511479168"/>
+        <c:crossAx val="547965184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="511479168"/>
+        <c:axId val="547965184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12164,7 +12254,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511477632"/>
+        <c:crossAx val="547963648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12294,7 +12384,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12627,6 +12717,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12636,7 +12729,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12969,6 +13062,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>229000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>231000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13002,7 +13098,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13335,6 +13431,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13344,7 +13443,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13677,6 +13776,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>639144.93698818795</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>521734.03754931345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13710,7 +13812,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14043,6 +14145,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14052,7 +14157,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14385,6 +14490,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>410144.93698818795</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>290734.03754931345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14406,11 +14514,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="511650048"/>
-        <c:axId val="511655936"/>
+        <c:axId val="547988224"/>
+        <c:axId val="547989760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="511650048"/>
+        <c:axId val="547988224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14420,14 +14528,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="511655936"/>
+        <c:crossAx val="547989760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="511655936"/>
+        <c:axId val="547989760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14438,7 +14546,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="511650048"/>
+        <c:crossAx val="547988224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14480,7 +14588,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14518,7 +14626,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14559,7 +14667,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14597,7 +14705,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14640,7 +14748,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14678,7 +14786,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14956,7 +15064,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14965,7 +15073,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB113"/>
+  <dimension ref="A1:AB114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18948,6 +19056,35 @@
         <v>391430.1755816536</v>
       </c>
     </row>
+    <row r="114" spans="1:9" ht="12.75">
+      <c r="A114" s="13">
+        <v>46234</v>
+      </c>
+      <c r="B114" s="18">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C114" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D114" s="15">
+        <v>713.52123405389671</v>
+      </c>
+      <c r="E114" s="15">
+        <v>178674.11619477134</v>
+      </c>
+      <c r="F114" s="15">
+        <v>500823.54292283044</v>
+      </c>
+      <c r="G114" s="15">
+        <v>224000</v>
+      </c>
+      <c r="H114" s="15">
+        <v>500823.54292283044</v>
+      </c>
+      <c r="I114" s="15">
+        <v>276823.54292283044</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18959,7 +19096,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24674,6 +24811,50 @@
         <v>80.686006638099158</v>
       </c>
     </row>
+    <row r="114" spans="1:14" ht="12.75">
+      <c r="A114" s="13">
+        <v>46234</v>
+      </c>
+      <c r="B114" s="18">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C114" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D114" s="15">
+        <v>713.52123405389671</v>
+      </c>
+      <c r="E114" s="15">
+        <v>186733.45705261352</v>
+      </c>
+      <c r="F114" s="15">
+        <v>523413.87513215444</v>
+      </c>
+      <c r="G114" s="15">
+        <v>231000</v>
+      </c>
+      <c r="H114" s="15">
+        <v>523413.87513215444</v>
+      </c>
+      <c r="I114" s="15">
+        <v>292413.87513215444</v>
+      </c>
+      <c r="J114" s="21">
+        <v>0</v>
+      </c>
+      <c r="K114" s="21">
+        <v>0.1858199982838401</v>
+      </c>
+      <c r="L114" s="21">
+        <v>0.64400005340576172</v>
+      </c>
+      <c r="M114" s="23">
+        <v>0.33763349715124008</v>
+      </c>
+      <c r="N114" s="21">
+        <v>55.036007935137903</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24685,7 +24866,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -31286,6 +31467,59 @@
         <v>101.62682554662496</v>
       </c>
     </row>
+    <row r="114" spans="1:17" ht="12.75">
+      <c r="A114" s="13">
+        <v>46234</v>
+      </c>
+      <c r="B114" s="18">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C114" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D114" s="15">
+        <v>713.52123405389671</v>
+      </c>
+      <c r="E114" s="15">
+        <v>186134.15716005411</v>
+      </c>
+      <c r="F114" s="15">
+        <v>521734.03754931345</v>
+      </c>
+      <c r="G114" s="15">
+        <v>231000</v>
+      </c>
+      <c r="H114" s="15">
+        <v>521734.03754931345</v>
+      </c>
+      <c r="I114" s="15">
+        <v>290734.03754931345</v>
+      </c>
+      <c r="J114" s="15">
+        <v>3.5380001068115234</v>
+      </c>
+      <c r="K114" s="15">
+        <v>2.687000036239624</v>
+      </c>
+      <c r="L114" s="19">
+        <v>3.5380001068115234</v>
+      </c>
+      <c r="M114" s="19">
+        <v>2.1180000305175781</v>
+      </c>
+      <c r="N114" s="21">
+        <v>48.239429998294135</v>
+      </c>
+      <c r="O114" s="21">
+        <v>74.461473454129361</v>
+      </c>
+      <c r="P114" s="21">
+        <v>78.51737781788178</v>
+      </c>
+      <c r="Q114" s="21">
+        <v>66.349664726624525</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1026,6 +1026,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1035,7 +1038,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1371,6 +1374,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>224000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>226000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1413,7 +1419,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1749,6 +1755,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1758,7 +1767,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2094,6 +2103,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>500823.54292283044</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>503538.23018617608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2136,7 +2148,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2472,6 +2484,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2481,7 +2496,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2817,6 +2832,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>276823.54292283044</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>277538.23018617608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2838,11 +2856,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="582754688"/>
-        <c:axId val="582756224"/>
+        <c:axId val="428224512"/>
+        <c:axId val="428227584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="582754688"/>
+        <c:axId val="428224512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2882,14 +2900,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="582756224"/>
+        <c:crossAx val="428227584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="582756224"/>
+        <c:axId val="428227584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2938,7 +2956,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="582754688"/>
+        <c:crossAx val="428224512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3068,7 +3086,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3404,6 +3422,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3413,7 +3434,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3749,6 +3770,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>224000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>226000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3782,7 +3806,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4118,6 +4142,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4127,7 +4154,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4463,6 +4490,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>500823.54292283044</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>503538.23018617608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4496,7 +4526,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4832,6 +4862,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4841,7 +4874,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5177,6 +5210,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>276823.54292283044</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>277538.23018617608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5198,11 +5234,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="678418688"/>
-        <c:axId val="548163584"/>
+        <c:axId val="451697664"/>
+        <c:axId val="485507840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="678418688"/>
+        <c:axId val="451697664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5212,14 +5248,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="548163584"/>
+        <c:crossAx val="485507840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="548163584"/>
+        <c:axId val="485507840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5230,7 +5266,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="678418688"/>
+        <c:crossAx val="451697664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5348,7 +5384,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5684,6 +5720,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5693,7 +5732,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6029,6 +6068,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>233000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6071,7 +6113,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6407,6 +6449,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6416,7 +6461,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6752,6 +6797,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>523413.87513215444</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>526160.79934388818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6794,7 +6842,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7130,6 +7178,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7139,7 +7190,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7475,6 +7526,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>292413.87513215444</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>293160.79934388818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7496,11 +7550,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="548191232"/>
-        <c:axId val="548193024"/>
+        <c:axId val="417873280"/>
+        <c:axId val="417879168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="548191232"/>
+        <c:axId val="417873280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7540,14 +7594,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548193024"/>
+        <c:crossAx val="417879168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="548193024"/>
+        <c:axId val="417879168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7596,7 +7650,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548191232"/>
+        <c:crossAx val="417873280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7726,7 +7780,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8062,6 +8116,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8071,7 +8128,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8407,6 +8464,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>233000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8440,7 +8500,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8776,6 +8836,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8785,7 +8848,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9121,6 +9184,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>523413.87513215444</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>526160.79934388818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9154,7 +9220,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9490,6 +9556,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9499,7 +9568,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9835,6 +9904,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>292413.87513215444</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>293160.79934388818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9856,11 +9928,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547692544"/>
-        <c:axId val="547694080"/>
+        <c:axId val="417894400"/>
+        <c:axId val="417895936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547692544"/>
+        <c:axId val="417894400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9870,14 +9942,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="547694080"/>
+        <c:crossAx val="417895936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547694080"/>
+        <c:axId val="417895936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9888,7 +9960,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="547692544"/>
+        <c:crossAx val="417894400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10006,7 +10078,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10342,6 +10414,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10351,7 +10426,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10687,6 +10762,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>233000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10729,7 +10807,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11065,6 +11143,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11074,7 +11155,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11410,6 +11491,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>521734.03754931345</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>524478.56459233991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11452,7 +11536,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11788,6 +11872,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11797,7 +11884,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12133,6 +12220,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>290734.03754931345</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>291478.56459233991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12154,11 +12244,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547963648"/>
-        <c:axId val="547965184"/>
+        <c:axId val="417927936"/>
+        <c:axId val="417929472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547963648"/>
+        <c:axId val="417927936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12198,14 +12288,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547965184"/>
+        <c:crossAx val="417929472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547965184"/>
+        <c:axId val="417929472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12254,7 +12344,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547963648"/>
+        <c:crossAx val="417927936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12384,7 +12474,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12720,6 +12810,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12729,7 +12822,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13065,6 +13158,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>231000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>233000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13098,7 +13194,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13434,6 +13530,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13443,7 +13542,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13779,6 +13878,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>521734.03754931345</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>524478.56459233991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13812,7 +13914,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14148,6 +14250,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14157,7 +14262,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14493,6 +14598,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>290734.03754931345</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>291478.56459233991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14514,11 +14622,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547988224"/>
-        <c:axId val="547989760"/>
+        <c:axId val="413787264"/>
+        <c:axId val="413788800"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547988224"/>
+        <c:axId val="413787264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14528,14 +14636,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="547989760"/>
+        <c:crossAx val="413788800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547989760"/>
+        <c:axId val="413788800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14546,7 +14654,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="547988224"/>
+        <c:crossAx val="413787264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14588,7 +14696,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14626,7 +14734,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14667,7 +14775,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14705,7 +14813,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14748,7 +14856,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14786,7 +14894,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -15064,7 +15172,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15073,7 +15181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB114"/>
+  <dimension ref="A1:AB115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -19085,6 +19193,35 @@
         <v>276823.54292283044</v>
       </c>
     </row>
+    <row r="115" spans="1:9" ht="12.75">
+      <c r="A115" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B115" s="18">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C115" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D115" s="15">
+        <v>712.50447300276869</v>
+      </c>
+      <c r="E115" s="15">
+        <v>179386.62066777411</v>
+      </c>
+      <c r="F115" s="15">
+        <v>503538.23018617608</v>
+      </c>
+      <c r="G115" s="15">
+        <v>226000</v>
+      </c>
+      <c r="H115" s="15">
+        <v>503538.23018617608</v>
+      </c>
+      <c r="I115" s="15">
+        <v>277538.23018617608</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19096,7 +19233,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24855,6 +24992,50 @@
         <v>55.036007935137903</v>
       </c>
     </row>
+    <row r="115" spans="1:14" ht="12.75">
+      <c r="A115" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B115" s="18">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C115" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D115" s="15">
+        <v>712.50447300276869</v>
+      </c>
+      <c r="E115" s="15">
+        <v>187445.96152561629</v>
+      </c>
+      <c r="F115" s="15">
+        <v>526160.79934388818</v>
+      </c>
+      <c r="G115" s="15">
+        <v>233000</v>
+      </c>
+      <c r="H115" s="15">
+        <v>526160.79934388818</v>
+      </c>
+      <c r="I115" s="15">
+        <v>293160.79934388818</v>
+      </c>
+      <c r="J115" s="21">
+        <v>3.9999485015869141E-3</v>
+      </c>
+      <c r="K115" s="21">
+        <v>0.15551665665346456</v>
+      </c>
+      <c r="L115" s="21">
+        <v>3.9999485015869141E-3</v>
+      </c>
+      <c r="M115" s="23">
+        <v>0.28202790570963121</v>
+      </c>
+      <c r="N115" s="21">
+        <v>55.142293902497926</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24866,7 +25047,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -31520,6 +31701,59 @@
         <v>66.349664726624525</v>
       </c>
     </row>
+    <row r="115" spans="1:17" ht="12.75">
+      <c r="A115" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B115" s="18">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C115" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D115" s="15">
+        <v>712.50447300276869</v>
+      </c>
+      <c r="E115" s="15">
+        <v>186846.66163305688</v>
+      </c>
+      <c r="F115" s="15">
+        <v>524478.56459233991</v>
+      </c>
+      <c r="G115" s="15">
+        <v>233000</v>
+      </c>
+      <c r="H115" s="15">
+        <v>524478.56459233991</v>
+      </c>
+      <c r="I115" s="15">
+        <v>291478.56459233991</v>
+      </c>
+      <c r="J115" s="15">
+        <v>2.9820001125335693</v>
+      </c>
+      <c r="K115" s="15">
+        <v>2.6749999523162842</v>
+      </c>
+      <c r="L115" s="19">
+        <v>3.5380001068115234</v>
+      </c>
+      <c r="M115" s="19">
+        <v>2.2260000705718994</v>
+      </c>
+      <c r="N115" s="21">
+        <v>44.283524022760979</v>
+      </c>
+      <c r="O115" s="21">
+        <v>64.40215697700657</v>
+      </c>
+      <c r="P115" s="21">
+        <v>73.812304204256705</v>
+      </c>
+      <c r="Q115" s="21">
+        <v>45.581862522506299</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
